--- a/data/qa/prospect_to_cash/invoice.xlsx
+++ b/data/qa/prospect_to_cash/invoice.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0007</t>
+          <t>KB-0079</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,50 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Invoice and Credit Memo Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HELP_GENERIC</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is an Invoice?</t>
+          <t>How is an invoice created for a standard customer order?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>An Invoice is the billing document issued to a customer after goods or services are delivered, stating the amount owed.</t>
+          <t>For a standard customer order, shipped but uninvoiced line or release quantities are selected by Order Invoicing/Credit Memo. Running that process calculates amounts, records invoice history, creates A/R invoice transactions, and produces the invoice.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>invoice,bill</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>bill</t>
-        </is>
-      </c>
+          <t>invoice, Order Invoicing/Credit Memo, shipped not invoiced</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -603,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>invoice.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Invoice and Credit Memo Module &gt; What creates an invoice</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -627,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -638,10 +640,402 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0080</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>What are the standard steps to invoice a customer order?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>First, confirm that the intended order line or release quantity has a posted shipping transaction. Then, run the To Be Invoiced Report to identify eligible lines and check invoice holds. Open Order Invoicing/Credit Memo, select Invoice, set the customer, order, date ranges, and print options. Preview totals, tax, freight, terms, ship-to, and currency as permitted, process with authorization, verify the invoice number and posted A/R transaction, and confirm document delivery using the site's process.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>create invoice, To Be Invoiced Report, invoice number, A/R transaction</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>invoice.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module &gt; Standard order invoicing steps</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0081</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How are invoice due dates and corrections handled?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Terms and invoice dates determine due scheduling according to the configured billing rules, and some terms permit multiple due dates. A posted invoice is a financial transaction, so a correction uses an approved credit/debit memo or return process rather than casual editing.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>invoice due date, credit memo, debit memo, invoice correction</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>invoice.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module &gt; Due date, amount, and corrections</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0082</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What is the process for correcting inventory and noninventory invoice errors?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>For inventory returns, RMA and material return processing may be required before a credit memo. For noninventory charges, A/R's Invoices, Debit and Credit Memos form has a different use.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>inventory returns, RMA, credit memo, noninventory charges</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>invoice.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module &gt; Due date, amount, and corrections</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0083</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Why is an expected invoice missing?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Check whether the order line was shipped, whether shipping posted, whether Invoice Hold is selected, whether a different consolidated or delivery-order billing route applies, and whether the invoicing process completed or stopped on an error. Compare shipment and invoice history before reporting that nothing was billed.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>invoice not generated, shipped not invoiced, billing error, invoice hold</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>invoice.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Invoice and Credit Memo Module &gt; Why an expected invoice is missing</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -658,39 +1052,489 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KB-0079</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>What triggers invoice creation after shipping?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0079</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>How do I generate an invoice for a shipped order?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0079</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>When does an invoice get created for a customer order?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0080</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>How do I invoice a customer order?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0080</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>What steps are involved in standard order invoicing?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0080</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Can you list the process for invoicing an order?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0081</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>How do I correct an invoice or set its due date?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0081</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>What determines invoice due dates and how do I fix mistakes?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0081</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>How are corrections made to posted invoices?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0082</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>How do I handle corrections for inventory versus noninventory invoices?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0082</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What's the difference in correcting inventory and noninventory invoice errors?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0082</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>How are inventory and noninventory invoice corrections processed?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0083</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Why didn't my invoice get created?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0083</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What could cause an invoice to be missing?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0083</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Why wasn't an invoice generated for my order?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
